--- a/src/attributions/attributions_ig_traj_97.xlsx
+++ b/src/attributions/attributions_ig_traj_97.xlsx
@@ -1002,43 +1002,43 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.09434788041138857</v>
+        <v>0.06186859918917142</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.406507924538936e-11</v>
+        <v>-2.743752641388712e-11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02013181251210497</v>
+        <v>-0.004488531808537719</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03840233256120568</v>
+        <v>0.04074996266205454</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07319719588597617</v>
+        <v>0.03938321614961738</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.003162618945822409</v>
+        <v>-0.006577439251853189</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1050,22 +1050,22 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05502737143311068</v>
+        <v>0.04328324774685843</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.01805115464110275</v>
+        <v>-0.02227129432177314</v>
       </c>
       <c r="W2" t="n">
-        <v>0.08574398092167063</v>
+        <v>-0.01190436281840869</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -1074,88 +1074,88 @@
         <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.04797530054156555</v>
+        <v>0.009403125860572301</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.001028821674430116</v>
+        <v>0.02897316562095329</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.006398256939101376</v>
+        <v>0.02906363036491267</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.02246120191343538</v>
+        <v>0.05084909649654318</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.06971935169157017</v>
+        <v>-0.005562207905654335</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.02114901880877596</v>
+        <v>0.0305960107149727</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.3513863084035338</v>
+        <v>0.1664893265679742</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.01593423400247702</v>
+        <v>-0.05756581706783485</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.2224999316669037</v>
+        <v>-0.05087643015707207</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
         <v>-0</v>
@@ -1164,16 +1164,16 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.02976565110622053</v>
+        <v>-0.01397773569231824</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.01754718844912015</v>
+        <v>-0.006318156777512945</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.02783194442997154</v>
+        <v>-0.01427410092786586</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,31 +1182,31 @@
         <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.0004586845546527046</v>
+        <v>0.007163727484107118</v>
       </c>
       <c r="BN2" t="n">
         <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.1239062976390406</v>
+        <v>0.006124233702998037</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1246887455566735</v>
+        <v>0.03260229220144024</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
         <v>-0</v>
@@ -1218,52 +1218,52 @@
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.1880420375875716</v>
+        <v>0.1078101165920672</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.0008806088671269872</v>
+        <v>-0.03449657147184609</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.03528606752043355</v>
+        <v>-0.0073394269959386</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD2" t="n">
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.06345480768927041</v>
+        <v>-0.05342925886580449</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.01401035888396312</v>
+        <v>0.0334323257142312</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.01607000757985386</v>
+        <v>-0.000755275588914952</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
         <v>-0</v>
@@ -1272,70 +1272,70 @@
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.01969912987765599</v>
+        <v>-0.01946913227197554</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.02598352580883261</v>
+        <v>0.02359223251618104</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.04603919526744064</v>
+        <v>0.02369311778249835</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.05041131354346526</v>
+        <v>-0.05671711794500371</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.04095626471224884</v>
+        <v>0.03645746434553641</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.002125383947344086</v>
+        <v>0.004023948156178139</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD2" t="n">
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.02549212941082261</v>
+        <v>-0.03461074064291845</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.03169293138993756</v>
+        <v>0.02876108352648398</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.04398595180924359</v>
+        <v>-0.03632473388202976</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
@@ -1353,70 +1353,70 @@
         <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.06237800320276927</v>
+        <v>-0.02344595482036638</v>
       </c>
       <c r="DP2" t="n">
         <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.005041371575536672</v>
+        <v>0.004909516018983253</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.00303394976042097</v>
+        <v>-0.02094227806318509</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
         <v>-0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.02363583333458356</v>
+        <v>0.04197408390716786</v>
       </c>
       <c r="DY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.0164020037834412</v>
+        <v>0.0273116943648214</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.002996203171079016</v>
+        <v>-0.007743282452356619</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.01828722236142075</v>
+        <v>-0.03471722342685574</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.02199997647977921</v>
+        <v>0.0272276766591313</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.03059033379890621</v>
+        <v>-0.0008657153537512082</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
@@ -1425,7 +1425,7 @@
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN2" t="n">
         <v>-0</v>
@@ -1434,22 +1434,22 @@
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.1199565008408914</v>
+        <v>-0.01747159252498082</v>
       </c>
       <c r="EQ2" t="n">
         <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.07064061943163945</v>
+        <v>-0.02835127640002734</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.009993068607193832</v>
+        <v>-0.009852989258884302</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
         <v>-0</v>
@@ -1458,28 +1458,28 @@
         <v>-0</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.06769423791477194</v>
+        <v>-0.06227522144698282</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.02983473870847285</v>
+        <v>0.04033982127584913</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.004044001357623623</v>
+        <v>-0.005213251515089526</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF2" t="n">
         <v>-0</v>
@@ -1488,16 +1488,16 @@
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.0539520523491171</v>
+        <v>-0.03042411750356098</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.03141745677551971</v>
+        <v>0.01970187989127586</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.01590202593074826</v>
+        <v>0.00530606441892255</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
@@ -1506,52 +1506,52 @@
         <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.03039422896475906</v>
+        <v>0.02099132461617529</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.01061990351260131</v>
+        <v>0.05109816231292422</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.0004602682602982453</v>
+        <v>-0.02830819127679613</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX2" t="n">
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.05835796229897641</v>
+        <v>-0.04108759885518318</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0.03426298446279576</v>
+        <v>0.007876194727798796</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
         <v>-0</v>
@@ -2137,52 +2137,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1657056242835222</v>
+        <v>0.02947832304041502</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02038711261801119</v>
+        <v>0.009641843772460112</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01343341814698383</v>
+        <v>-0.004342417290850968</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07560760401601024</v>
+        <v>0.02638291707097864</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06745769922491446</v>
+        <v>0.02910003161951813</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01150649278041577</v>
+        <v>-0.006677085726476037</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -2194,76 +2194,76 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07266220021961219</v>
+        <v>0.0185791943463417</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.04633218289096432</v>
+        <v>-0.005136390055803942</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02924141474702423</v>
+        <v>-0.00335286356418119</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.05645018917526724</v>
+        <v>0.001764377085287886</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.01946833310554934</v>
+        <v>0.01574877143248245</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.02177476726136142</v>
+        <v>0.01148967201131589</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.003124014977477572</v>
+        <v>0.03164325709025053</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.02773890368321493</v>
+        <v>0.001034423233423175</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.00693969882979095</v>
+        <v>0.03343579131968751</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2272,19 +2272,19 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.3573720309601651</v>
+        <v>0.06863052433981583</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.05421541166391632</v>
+        <v>-0.002086232024137983</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1924461466591297</v>
+        <v>-0.02409954957292341</v>
       </c>
       <c r="AY4" t="n">
         <v>-0</v>
@@ -2299,46 +2299,46 @@
         <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.03403641146282001</v>
+        <v>-0.0152183472462178</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.02306888601193056</v>
+        <v>-0.001721715461312925</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.04398690591932482</v>
+        <v>-0.01236537888331621</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.08394554045879092</v>
+        <v>0.01362316507138404</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.05597217122145667</v>
+        <v>0.005900408052712977</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.1592016637979533</v>
+        <v>0.03754914875213702</v>
       </c>
       <c r="BQ4" t="n">
         <v>-0</v>
@@ -2356,43 +2356,43 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1787682726382635</v>
+        <v>0.05765803351712695</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.02371388216099592</v>
+        <v>-0.01393104104814516</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.06679413622275558</v>
+        <v>0.003855590653791621</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
         <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.07488789813965988</v>
+        <v>-0.02062566218148698</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.003401897892630264</v>
+        <v>0.01534250772624198</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.009181207903950613</v>
+        <v>0.005251177230676655</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
@@ -2401,7 +2401,7 @@
         <v>-0</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
         <v>-0</v>
@@ -2410,43 +2410,43 @@
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.03820989903262816</v>
+        <v>-0.01010530389266189</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.01786730674890456</v>
+        <v>0.004444921908041462</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.03894724035066945</v>
+        <v>0.01620565907705489</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.06176570018068037</v>
+        <v>-0.02077175033253884</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.01346070162889292</v>
+        <v>0.01643131228785805</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.001333049245981499</v>
+        <v>0.008173895466512834</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
@@ -2461,19 +2461,19 @@
         <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.02143565043677613</v>
+        <v>0.001440003847797746</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.02364876089818574</v>
+        <v>0.0003273698950120281</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01117935278582428</v>
+        <v>-0.002799601991292699</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
@@ -2482,88 +2482,88 @@
         <v>-0</v>
       </c>
       <c r="DL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.06117426881550261</v>
+        <v>-0.0171461315341824</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.04210652788283065</v>
+        <v>-0.02023593022081272</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.001598253238636514</v>
+        <v>-0.02267478755342402</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.01123280976085185</v>
+        <v>0.03189930136374814</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.03161575652286874</v>
+        <v>0.01245789717313675</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.0347505752261054</v>
+        <v>-0.02957384830934764</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.04302776711017425</v>
+        <v>0.0007373018816140655</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.01352917111618041</v>
+        <v>0.007559774722726587</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.002602115534663811</v>
+        <v>0.01790072566252164</v>
       </c>
       <c r="EK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL4" t="n">
         <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
@@ -2572,22 +2572,22 @@
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.08080047572074987</v>
+        <v>-0.007220052612767931</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.02207356398421021</v>
+        <v>0.001926659725071348</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.04195156923717229</v>
+        <v>0.002024832985538699</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>-0</v>
@@ -2599,16 +2599,16 @@
         <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.06565708378514638</v>
+        <v>-0.02313606063172241</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.002273937633323122</v>
+        <v>0.01951966732433022</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.01332826395097836</v>
+        <v>0.002205731410184889</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
@@ -2623,19 +2623,19 @@
         <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.02851760508012226</v>
+        <v>0.00252001365677039</v>
       </c>
       <c r="FI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.03163337230346011</v>
+        <v>0.004431900251338793</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.05480133947747115</v>
+        <v>-0.01391147960078033</v>
       </c>
       <c r="FL4" t="n">
         <v>-0</v>
@@ -2644,34 +2644,34 @@
         <v>-0</v>
       </c>
       <c r="FN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO4" t="n">
         <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.06263986131778876</v>
+        <v>0.01309668083181549</v>
       </c>
       <c r="FR4" t="n">
         <v>0</v>
       </c>
       <c r="FS4" t="n">
-        <v>-0.08559365028579977</v>
+        <v>0.03319514910608914</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.02177135930566357</v>
+        <v>-0.03421209355064037</v>
       </c>
       <c r="FU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
         <v>0</v>
@@ -2680,28 +2680,28 @@
         <v>-0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.04554442655523278</v>
+        <v>-0.00185926440426463</v>
       </c>
       <c r="GA4" t="n">
         <v>-0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.04116165982373821</v>
+        <v>-0.01015054056334888</v>
       </c>
       <c r="GC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF4" t="n">
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4111320969506546</v>
+        <v>0.120754432540281</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,10 +2718,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02358256586918858</v>
+        <v>-0.01838189815031301</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1792608810627166</v>
+        <v>-0.03011253223835487</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -2736,22 +2736,22 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2379626069664717</v>
+        <v>0.1335539491580982</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002418477277175751</v>
+        <v>-0.0319793329340297</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.07842125405032033</v>
+        <v>-0.00661822276511028</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-0</v>
@@ -2763,49 +2763,49 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02817595103259742</v>
+        <v>0.02903219446657623</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1276809088937728</v>
+        <v>-0.01959432736199001</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.0827236656829249</v>
+        <v>-0.002426123142332981</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.09940724559356623</v>
+        <v>-0.003656705611415597</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.01858027273917465</v>
+        <v>0.03690216355388647</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.02961551475782003</v>
+        <v>-0.005943551782565218</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.08854244585182115</v>
+        <v>0.06116695977201107</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2826,25 +2826,25 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.05130078041211709</v>
+        <v>0.02477827263943238</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.2252444113146931</v>
+        <v>-0.04132264407839838</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.6568588836858873</v>
+        <v>0.2310202065655838</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
@@ -2853,16 +2853,16 @@
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.03937457979777849</v>
+        <v>-0.07167244462567159</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.2419292571258394</v>
+        <v>-0.05810008462584259</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1161815682262236</v>
+        <v>-0.004732951203715429</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,52 +2880,52 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.07781674359735101</v>
+        <v>-0.02586572456944345</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.07196153337767504</v>
+        <v>-0.02477687012216788</v>
       </c>
       <c r="BI5" t="n">
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.2258279380520328</v>
+        <v>0.007366579902495198</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
         <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1033566897738419</v>
+        <v>0.07153327481609587</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.05048835056374159</v>
+        <v>0.008561573510297675</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.3007166005969449</v>
+        <v>0.1529198288789622</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,16 +2934,16 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.03666796558690986</v>
+        <v>-0.0238530372747193</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.02826833632720982</v>
+        <v>-0.0402378921638415</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
@@ -2952,88 +2952,88 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1546313974281505</v>
+        <v>-0.08523775075081158</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.04070419521705373</v>
+        <v>0.009500292631169357</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.1184715981077245</v>
+        <v>0.04031255349522377</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.006539323907415966</v>
+        <v>-0.06254634558904083</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0265989421888663</v>
+        <v>0.0296694220022906</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.1006558601153261</v>
+        <v>0.04097653027262035</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT5" t="n">
         <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1064990828042175</v>
+        <v>-0.0844406378134922</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.03773375859253105</v>
+        <v>0.0069314894337812</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.1286154949057224</v>
+        <v>0.04332412167396352</v>
       </c>
       <c r="DB5" t="n">
         <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.01871537356717067</v>
+        <v>-0.01047979447992904</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
@@ -3042,40 +3042,40 @@
         <v>-0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.02369923939852183</v>
+        <v>-0.01682674529359223</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.001558429664727605</v>
+        <v>0.03362563205370084</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.06304488579381003</v>
+        <v>-0.04830571355710719</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.02556134540174183</v>
+        <v>0.01141069975637595</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.08860122584920155</v>
+        <v>-0.002508411611289687</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
@@ -3087,7 +3087,7 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.06608165992296255</v>
+        <v>0.03894554796499349</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
@@ -3096,52 +3096,52 @@
         <v>0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.08418786500915654</v>
+        <v>-0.007596356111195973</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.07266603767056611</v>
+        <v>-0.09747112502355625</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
         <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.05943105407897484</v>
+        <v>-0.0348137453041619</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.04863504922593821</v>
+        <v>-0.01303652979036637</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.08056488584251942</v>
+        <v>0.02525289229714641</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.1160158850719127</v>
+        <v>-0.03849299103265789</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,52 +3150,52 @@
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.09288342740707775</v>
+        <v>-0.03054313582133479</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.2621194699314724</v>
+        <v>0.04711685755691363</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1008679973981888</v>
+        <v>-0.09774603314296795</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
         <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.03952604944732149</v>
+        <v>0.0001455507204701505</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.126848413033026</v>
+        <v>0.04023946232023423</v>
       </c>
       <c r="FD5" t="n">
         <v>-0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.07456720861828821</v>
+        <v>-0.05647460667471774</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
@@ -3204,55 +3204,55 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.07580627590038916</v>
+        <v>0.01884249047070964</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0.0006429128336200786</v>
+        <v>-0.0177151921033388</v>
       </c>
       <c r="FM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.1041418280789491</v>
+        <v>0.05048805152888079</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.1162234886281514</v>
+        <v>-0.005736324342308857</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.01186438839749675</v>
+        <v>-0.0007528822294993394</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.0539387406467447</v>
+        <v>-0.03045709524957614</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
@@ -3261,13 +3261,13 @@
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0.0803452366861732</v>
+        <v>-0.0002789763098037011</v>
       </c>
       <c r="GE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>0</v>
@@ -3281,13 +3281,13 @@
         <v>-0</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.01042869137001849</v>
+        <v>-0.004446032088459234</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1230302688064303</v>
+        <v>0.07959189714482634</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.03309095389595627</v>
+        <v>-0.03267894855532926</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3302,58 +3302,58 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.03453155756518091</v>
+        <v>-0.01212871269752766</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1517299894060621</v>
+        <v>0.07188344405299255</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03717885029209736</v>
+        <v>-0.01613525550029596</v>
       </c>
       <c r="O6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.04286031727670936</v>
+        <v>-0.01071839507657378</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06683697607835783</v>
+        <v>0.03301642442590663</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.006276581202338312</v>
+        <v>-0.004446965553429369</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -3362,67 +3362,67 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.027494840737069e-11</v>
+        <v>1.011110551458153e-12</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.03284524369634274</v>
+        <v>-0.03122424901285726</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.006202485568957438</v>
+        <v>0.04383940193092243</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.006948339947157798</v>
+        <v>-0.04611985824856239</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.05225979522733523</v>
+        <v>0.0744429266432247</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.01697164270976599</v>
+        <v>-0.04053659044848429</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.1068741668298867</v>
+        <v>-0.08570340729717567</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1067173608473289</v>
+        <v>0.155068237797062</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.1752015384969609</v>
+        <v>-0.1090478554507375</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
@@ -3431,7 +3431,7 @@
         <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>0</v>
@@ -3443,13 +3443,13 @@
         <v>-0</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.03553269029885878</v>
+        <v>0.003826749041838994</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.04586376392516243</v>
+        <v>-0.06140143563224584</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.01782308281531692</v>
+        <v>-0.08622042428415137</v>
       </c>
       <c r="BH6" t="n">
         <v>-0</v>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>-0</v>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.02810065995097656</v>
+        <v>0.02546209698643471</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.03707319930836066</v>
+        <v>0.05556669272833568</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.07365042183451745</v>
+        <v>0.08681655475959722</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
@@ -3485,85 +3485,85 @@
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.09572020751117027</v>
+        <v>-0.05053460733848143</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.1139443380296394</v>
+        <v>0.1009022726215587</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.105030260879338</v>
+        <v>-0.04326493680195397</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE6" t="n">
         <v>0</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.04136965437156848</v>
+        <v>0.03370859365698559</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.05860064060659846</v>
+        <v>-0.01576236075648284</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.002681708435055325</v>
+        <v>0.006487484550541673</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
         <v>0</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.01759365352553728</v>
+        <v>0.004931890860612268</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.003761985869944934</v>
+        <v>0.04148737537330235</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.04298278634928088</v>
+        <v>0.1024074759267353</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>0</v>
@@ -3578,22 +3578,22 @@
         <v>-0</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.02402343072642254</v>
+        <v>0.02871168335319034</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.05525912753748603</v>
+        <v>-0.02091194452988487</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.01067427201279725</v>
+        <v>0.01798026224909228</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD6" t="n">
         <v>-0</v>
@@ -3602,70 +3602,70 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.006924391241504014</v>
+        <v>0.01733851167337069</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.04518675131906493</v>
+        <v>-0.04536770975444546</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.002325248967013727</v>
+        <v>-0.00314135534797664</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM6" t="n">
         <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO6" t="n">
         <v>0</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.01323490806876642</v>
+        <v>-0.0008464724998759148</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.02135387071409757</v>
+        <v>-0.01080709369261472</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.03351203764498438</v>
+        <v>0.04013664363804555</v>
       </c>
       <c r="DS6" t="n">
         <v>-0</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.02432039550455034</v>
+        <v>-0.03476141710111016</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.03258441927702255</v>
+        <v>-0.05126251463749752</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.04033800848683149</v>
+        <v>-0.02643883420581992</v>
       </c>
       <c r="EB6" t="n">
         <v>-0</v>
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="ED6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE6" t="n">
         <v>0</v>
@@ -3686,148 +3686,148 @@
         <v>0</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.05036555373823945</v>
+        <v>0.006325162947262151</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.06849696891146201</v>
+        <v>-0.01602356230110673</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.02389267661257155</v>
+        <v>-0.02937528220733645</v>
       </c>
       <c r="EK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.05145098080514049</v>
+        <v>-0.01288738131411287</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0.03317768953609478</v>
+        <v>-0.05814462362073748</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01934575852058064</v>
+        <v>0.02243671619373056</v>
       </c>
       <c r="ET6" t="n">
         <v>-0</v>
       </c>
       <c r="EU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
         <v>0</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.02728735686670834</v>
+        <v>0.03047294913828346</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0.05547776958395853</v>
+        <v>-0.0262818547620855</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.002181511755434767</v>
+        <v>0.01286086969810502</v>
       </c>
       <c r="FC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0290189604768337</v>
+        <v>0.05330814819556019</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.0245504035948593</v>
+        <v>-0.01055893380264708</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.02152438931602076</v>
+        <v>-0.03513914268469186</v>
       </c>
       <c r="FL6" t="n">
         <v>0</v>
       </c>
       <c r="FM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP6" t="n">
         <v>0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.009500815669758684</v>
+        <v>-0.0001642813226298364</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.004828019153648192</v>
+        <v>0.0005490717757293683</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.01299274040415152</v>
+        <v>-0.005648959565056171</v>
       </c>
       <c r="FU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV6" t="n">
         <v>0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
         <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.02296848289731963</v>
+        <v>0.02798201892812602</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.01099024757194601</v>
+        <v>-0.07885151841507702</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
         <v>0</v>
@@ -4416,19 +4416,19 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1044088754940439</v>
+        <v>0.1245625774450847</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.07832780177233127</v>
+        <v>-0.0278010441180578</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.03179716969707614</v>
+        <v>-0.04126126972804039</v>
       </c>
       <c r="G8" t="n">
         <v>-0</v>
@@ -4440,28 +4440,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06241878453672817</v>
+        <v>0.1548462485793331</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.06898440328844287</v>
+        <v>-0.06633256104737401</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.03537547505625575</v>
+        <v>-0.03649695490577651</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -4470,115 +4470,115 @@
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02822544101302507</v>
+        <v>0.0730810760896822</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.01329592300807173</v>
+        <v>-0.02843484051896291</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02479033644328613</v>
+        <v>0.03536487319110487</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.01185824858284322</v>
+        <v>0.009852079999877143</v>
       </c>
       <c r="AD8" t="n">
         <v>-0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.004889007696877502</v>
+        <v>0.02177960324952416</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.01243221302392616</v>
+        <v>-0.03385373608354249</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0463589044133096</v>
+        <v>0.02224401838927392</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.01140285256105663</v>
+        <v>-0.03058519956104243</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.004666920676855</v>
+        <v>-0.04526776726535579</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT8" t="n">
         <v>-0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1421593541027407</v>
+        <v>0.2845302085986567</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.06412795111771523</v>
+        <v>-0.1344587339700636</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.04760655275956677</v>
+        <v>-0.1288558781116234</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB8" t="n">
         <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.02954556964014671</v>
+        <v>-0.04786972417622889</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,52 +4587,52 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.06428990002848578</v>
+        <v>-0.02276196893965952</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.002455262544412961</v>
+        <v>0.007483804451995597</v>
       </c>
       <c r="BI8" t="n">
         <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.04997161291803339</v>
+        <v>0.09374012617849825</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01918775826261736</v>
+        <v>0.101637002405064</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.02655585124963087</v>
+        <v>0.07461730089805997</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.06474140160821251</v>
+        <v>0.1882428598852298</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,16 +4641,16 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.02395678789920924</v>
+        <v>-0.05544328961769689</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.005559005697554911</v>
+        <v>-0.0147197414846703</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
         <v>-0</v>
@@ -4659,25 +4659,25 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.02389679677547089</v>
+        <v>-0.05009258598863145</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
         <v>0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.01898949191757087</v>
+        <v>0.02747313394140785</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.01598554641011758</v>
+        <v>0.0237680892656351</v>
       </c>
       <c r="CJ8" t="n">
         <v>-0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL8" t="n">
         <v>-0</v>
@@ -4686,19 +4686,19 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.009847451096038753</v>
+        <v>-0.04592080360370205</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.00564786832138825</v>
+        <v>0.04482142255886529</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.01262133163453199</v>
+        <v>-0.004287347504720611</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
@@ -4707,31 +4707,31 @@
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.01280811615875435</v>
+        <v>-0.04856113343197972</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.01591138536799253</v>
+        <v>0.01648967301688054</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.02476848771374622</v>
+        <v>0.03048043591513906</v>
       </c>
       <c r="DB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
@@ -4740,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0169096632894237</v>
+        <v>-0.04325833141929963</v>
       </c>
       <c r="DG8" t="n">
         <v>-0</v>
@@ -4749,40 +4749,40 @@
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.03645997544895128</v>
+        <v>0.01588670992508217</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.00440046913448224</v>
+        <v>0.005402724765693583</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.01310629503999035</v>
+        <v>-0.0009730005389386716</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.03513449761250956</v>
+        <v>-0.03754110206450902</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0.03774819159691402</v>
+        <v>-0.01009266497309916</v>
       </c>
       <c r="DT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.01402852500461805</v>
+        <v>0.0456764052888407</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
@@ -4803,43 +4803,43 @@
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.03825001086770231</v>
+        <v>-0.1095997780094255</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.003354356606631699</v>
+        <v>0.01046021655868766</v>
       </c>
       <c r="EC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.008639683863850058</v>
+        <v>0.001419379053367551</v>
       </c>
       <c r="EH8" t="n">
         <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.004530740191146274</v>
+        <v>-0.02954330685095755</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.01079340676095349</v>
+        <v>0.0172546925939134</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
@@ -4848,7 +4848,7 @@
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0101026928726536</v>
+        <v>-0.007459967981989922</v>
       </c>
       <c r="EQ8" t="n">
         <v>-0</v>
@@ -4857,16 +4857,16 @@
         <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.005773292019777605</v>
+        <v>-0.08446489085727482</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.01916460486535386</v>
+        <v>0.03802116677323011</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
         <v>-0</v>
@@ -4875,7 +4875,7 @@
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.00534733172397182</v>
+        <v>-0.06239947894183864</v>
       </c>
       <c r="EZ8" t="n">
         <v>-0</v>
@@ -4884,16 +4884,16 @@
         <v>0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.01301465422396969</v>
+        <v>0.01161561847221403</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.02489470023506182</v>
+        <v>0.0168022181364018</v>
       </c>
       <c r="FD8" t="n">
         <v>-0</v>
       </c>
       <c r="FE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF8" t="n">
         <v>-0</v>
@@ -4902,19 +4902,19 @@
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.03977926383491597</v>
+        <v>-0.03974445076713069</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.04684466210833624</v>
+        <v>0.06805727974900545</v>
       </c>
       <c r="FL8" t="n">
-        <v>-0.001283688512195837</v>
+        <v>-0.01200487710360297</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
@@ -4926,37 +4926,37 @@
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.003537697709897292</v>
+        <v>0.01440570305723765</v>
       </c>
       <c r="FR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS8" t="n">
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.00180963413776773</v>
+        <v>-0.02240684250199756</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.02403724112568531</v>
+        <v>-0.07088560746612228</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
         <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.0107644234051965</v>
+        <v>-0.04724619343786515</v>
       </c>
       <c r="GA8" t="n">
         <v>0</v>
@@ -4968,7 +4968,7 @@
         <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.01969228147768452</v>
+        <v>0.03492243041870547</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
@@ -4977,7 +4977,7 @@
         <v>0</v>
       </c>
       <c r="GG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -4985,16 +4985,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3554834741765339</v>
+        <v>0.1857427730892109</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.169731077660396</v>
+        <v>-0.06458965221550002</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.02925855084210003</v>
+        <v>0.003210902295009671</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5012,19 +5012,19 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2660640747201239</v>
+        <v>0.1973868845786854</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1576153899870753</v>
+        <v>-0.07942048617332582</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.09504239975096841</v>
+        <v>-0.008032885882509147</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9" t="n">
         <v>-0</v>
@@ -5036,79 +5036,79 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1256195605694</v>
+        <v>0.06634421151174738</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.02731500908129626</v>
+        <v>-0.04311080167891121</v>
       </c>
       <c r="W9" t="n">
-        <v>0.07527514365905036</v>
+        <v>-0.04500917933411637</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.01645158866193547</v>
+        <v>0.005054832018004388</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.005078399719614066</v>
+        <v>0.04062432843443581</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.001315938608642154</v>
+        <v>0.008393299447347553</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.06003749711718513</v>
+        <v>0.08445804081036985</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.05840578067163657</v>
+        <v>-0.04566260018421147</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.008468129009323451</v>
+        <v>0.06546756647751843</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
@@ -5117,19 +5117,19 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.496720579839677</v>
+        <v>0.2196249388152272</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.01028826099892909</v>
+        <v>-0.06549281092904093</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1896024279842506</v>
+        <v>-0.05659540273983221</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
@@ -5138,7 +5138,7 @@
         <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>-0</v>
@@ -5147,16 +5147,16 @@
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.00137307204550069</v>
+        <v>-0.0193393177157656</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.1076704215069631</v>
+        <v>-0.03036561404577283</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1847450806684384</v>
+        <v>-0.06007835184347531</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.02901419610113873</v>
+        <v>-0.007767610670285491</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.1019622929282801</v>
+        <v>-0.0142849719225585</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.05579015769965312</v>
+        <v>0.03484482022971511</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5198,25 +5198,25 @@
         <v>-0</v>
       </c>
       <c r="BU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2897436781094492</v>
+        <v>0.1782849152978268</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.03482228300798591</v>
+        <v>-0.05666126903554969</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.06805188594878923</v>
+        <v>-0.02581901687363032</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
@@ -5228,22 +5228,22 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1097648349225111</v>
+        <v>-0.08407285817535798</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.03784643981313174</v>
+        <v>0.0600056618354936</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.03009342085257126</v>
+        <v>-0.01420522961787968</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5255,19 +5255,19 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.01975091819071018</v>
+        <v>-0.03013925670351257</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.0501285777795004</v>
+        <v>0.07668687702573143</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.08701250091406273</v>
+        <v>0.03626391686567088</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5276,28 +5276,28 @@
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.09285488691778247</v>
+        <v>-0.07817011972677604</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.05614517195302422</v>
+        <v>0.06398418510267585</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.03044868179593049</v>
+        <v>-0.007522105887551247</v>
       </c>
       <c r="DA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
@@ -5309,19 +5309,19 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.03981737854758793</v>
+        <v>-0.0411606843982408</v>
       </c>
       <c r="DG9" t="n">
         <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.02294341138825893</v>
+        <v>0.01929431025938891</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.01882166786357043</v>
+        <v>-0.04682275633535876</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
         <v>-0</v>
@@ -5333,22 +5333,22 @@
         <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.05989610789615694</v>
+        <v>-0.03372086948549852</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.01832516694979579</v>
+        <v>0.03915346542302428</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.05977427441375336</v>
+        <v>-0.02121716951158173</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
@@ -5360,25 +5360,25 @@
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0219461072425613</v>
+        <v>0.05957306084515467</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.005805823631992377</v>
+        <v>-0.02555760322202223</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.0456826251742486</v>
+        <v>-0.00128887472798976</v>
       </c>
       <c r="EB9" t="n">
         <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
         <v>0</v>
@@ -5387,79 +5387,79 @@
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.05729727527861347</v>
+        <v>-0.05179275304580865</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0594454127493977</v>
+        <v>0.03941580653757532</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.04448801897265706</v>
+        <v>0.003250047631214763</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.1027157712849295</v>
+        <v>-0.01646581531652098</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.06005912712129366</v>
+        <v>0.0204837241082408</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.02968712205254273</v>
+        <v>-0.03074014799075924</v>
       </c>
       <c r="ET9" t="n">
         <v>-0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.1031650358848905</v>
+        <v>-0.09239112162782871</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.06711076672284963</v>
+        <v>0.07067167700669603</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.03639501572418339</v>
+        <v>-0.01985434529660994</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
@@ -5468,19 +5468,19 @@
         <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.02321540961129795</v>
+        <v>-0.05553900708520166</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.09002814056550335</v>
+        <v>0.06554359668121283</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.05740868793883689</v>
+        <v>-0.02290310938553972</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
@@ -5489,52 +5489,52 @@
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
         <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.004054593101786273</v>
+        <v>0.002450347589889461</v>
       </c>
       <c r="FR9" t="n">
         <v>-0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.03829828290064572</v>
+        <v>0.02380181844350561</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.01123257066644982</v>
+        <v>-0.01227890462821259</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX9" t="n">
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.04346364654687313</v>
+        <v>-0.06579932600138176</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.05834508309368545</v>
+        <v>0.005534138028133401</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
         <v>-0</v>
@@ -5543,10 +5543,10 @@
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,25 +5554,25 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2284679913330576</v>
+        <v>0.2333232972591792</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.03452672063430167</v>
+        <v>-0.003246522302366387</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1074085798484415</v>
+        <v>-0.04418390990740133</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -5581,34 +5581,34 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1602336492809228</v>
+        <v>0.2845221509295771</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.02820327464291416</v>
+        <v>-0.05003744523342316</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1398325992482347</v>
+        <v>-0.02347120892416843</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.04278282770678281</v>
+        <v>0.0579390120466598</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -5617,40 +5617,40 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.01558406038026031</v>
+        <v>-0.03893229500250636</v>
       </c>
       <c r="X10" t="n">
-        <v>0.007785440844215277</v>
+        <v>0.01896274418936863</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.752436177073586e-11</v>
+        <v>-1.291757629876161e-11</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.004832993455164162</v>
+        <v>0.01439513812708765</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0008387144886187044</v>
+        <v>-0.001987529223848887</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>-0</v>
@@ -5662,22 +5662,22 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02870283992388174</v>
+        <v>0.0484338228683596</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.02668174624332875</v>
+        <v>0.0266593005696161</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.04714194074961432</v>
+        <v>-0.03204189259798992</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
@@ -5686,28 +5686,28 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.21531647732545</v>
+        <v>0.269610095432761</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.0605668347581087</v>
+        <v>-0.1339110057292457</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.135293036016447</v>
+        <v>-0.04497312687320856</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>0</v>
@@ -5716,7 +5716,7 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.09047462026011717</v>
+        <v>0.03949063378257763</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,52 +5725,52 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.05497979133580059</v>
+        <v>-0.03608993618464439</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.04577604159390475</v>
+        <v>-0.05813146201663796</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.08196687447206813</v>
+        <v>0.02540499965286425</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.02506620431395474</v>
+        <v>0.04919408054805748</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01465682322987735</v>
+        <v>-0.007994247526760171</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1003944587297585</v>
+        <v>0.2305599357593432</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
@@ -5779,64 +5779,64 @@
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.03008907212187986</v>
+        <v>-0.03022294844014277</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.04767340727559557</v>
+        <v>-0.02160666657124662</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.05607637536361321</v>
+        <v>-0.09603247538778703</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.009925109835392729</v>
+        <v>0.001321634626218049</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.04935885380603319</v>
+        <v>0.03889807745657324</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.005679436698296375</v>
+        <v>-0.08626479223779478</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.01601815944084762</v>
+        <v>0.0471341597054543</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.02310457919597958</v>
+        <v>0.03732043484521764</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
@@ -5845,31 +5845,31 @@
         <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.04179292895874197</v>
+        <v>-0.09678488848816998</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.004990264128719448</v>
+        <v>-0.01178952293765864</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.05057815540814781</v>
+        <v>0.03581736673295139</v>
       </c>
       <c r="DB10" t="n">
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
@@ -5878,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.03294801804574252</v>
+        <v>-0.034699336708139</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
@@ -5887,40 +5887,40 @@
         <v>-0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01184934108385071</v>
+        <v>-0.1063204255980823</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-0.00501746531966426</v>
+        <v>0.02912658974894706</v>
       </c>
       <c r="DK10" t="n">
         <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.01618948341817553</v>
+        <v>-0.06988510020644657</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.006473076650608581</v>
+        <v>0.02425555799089339</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.003511936668645187</v>
+        <v>-0.03303347960943202</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
         <v>-0</v>
@@ -5932,7 +5932,7 @@
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.02959022693414754</v>
+        <v>0.0131433626269949</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,10 +5941,10 @@
         <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.03051165691329462</v>
+        <v>0.0406752883657733</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0.03574908678776404</v>
+        <v>-0.08104216383929508</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
@@ -5959,22 +5959,22 @@
         <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.03713364414683632</v>
+        <v>0.001168552960086614</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.01766434772990117</v>
+        <v>-0.04330076857215757</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.03631483230744378</v>
+        <v>0.01708669497859122</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
         <v>-0</v>
@@ -5983,64 +5983,64 @@
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.01979629546353126</v>
+        <v>-0.01909434657559568</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.02456015816617374</v>
+        <v>-0.1030155607824504</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.02435776267337503</v>
+        <v>0.05772417352640383</v>
       </c>
       <c r="EU10" t="n">
         <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.04311444157490446</v>
+        <v>-0.112809036121908</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.003213891078588824</v>
+        <v>-0.0189425468333347</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.05233424280739479</v>
+        <v>0.03247275406961482</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.01075891408832467</v>
+        <v>-0.1323725391625329</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
@@ -6049,37 +6049,37 @@
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.02793878544877366</v>
+        <v>0.09845453873037306</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.04202999971864651</v>
+        <v>0.01293961020519131</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0005582140366675317</v>
+        <v>0.002236592784770181</v>
       </c>
       <c r="FR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS10" t="n">
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.002758434040657075</v>
+        <v>-0.006416724911190989</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0411649266870156</v>
+        <v>-0.0251972772798837</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
@@ -6088,34 +6088,34 @@
         <v>-0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0003738339304476674</v>
+        <v>-0.009933429715160917</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.0463561752190459</v>
+        <v>-0.009499599997713685</v>
       </c>
       <c r="GE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,16 +6123,16 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4869774741774341</v>
+        <v>0.2238672076106714</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.154390742675009</v>
+        <v>-0.1160512523109861</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1151615655797581</v>
+        <v>-0.02799938155181934</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -6150,16 +6150,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3157799274773701</v>
+        <v>0.2253906823201467</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1374156125648737</v>
+        <v>-0.1399826366179387</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1271922506046665</v>
+        <v>-0.05645549446881182</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -6171,76 +6171,76 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1567461385501538</v>
+        <v>0.0548297766992024</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0410652096679272</v>
+        <v>-0.04367128142940455</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02679319549570661</v>
+        <v>-0.04881240522517414</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.008884469012214199</v>
+        <v>-0.006694847012705324</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0003389367582183338</v>
+        <v>0.0115872222831988</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.089148499428183e-12</v>
+        <v>-3.179488475065011e-11</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.08210360349654811</v>
+        <v>0.08613608214002991</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.04665885595132206</v>
+        <v>-0.02162445322432877</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.0541686556080892</v>
+        <v>0.05123230735912746</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -6249,7 +6249,7 @@
         <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
@@ -6258,16 +6258,16 @@
         <v>-0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.5219737528584432</v>
+        <v>0.2541781491254764</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.004416026166317888</v>
+        <v>-0.0687019695801382</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.03580393169993254</v>
+        <v>-0.1095865822826424</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -6276,25 +6276,25 @@
         <v>-0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.03346750916934693</v>
+        <v>-0.02304634935181229</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.1065414461962903</v>
+        <v>-0.05441770994388096</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.2052451839703452</v>
+        <v>-0.05433101295215969</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6303,31 +6303,31 @@
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.07601678237639317</v>
+        <v>0.01122674835298912</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.07021626114810187</v>
+        <v>0.01608223598614195</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.09700267887941633</v>
+        <v>0.03713687038258395</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6336,46 +6336,46 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.2718983438228091</v>
+        <v>0.1874074858432394</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
-        <v>-0.004504023944255808</v>
+        <v>-0.06949027485587543</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.004296569911264418</v>
+        <v>-0.04438889566566722</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1242938867039773</v>
+        <v>-0.0824916969960254</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.01667768510264707</v>
+        <v>0.06480166388086642</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.009942366002800846</v>
+        <v>-0.003473243544576814</v>
       </c>
       <c r="CI11" t="n">
         <v>-0</v>
@@ -6387,25 +6387,25 @@
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.005256408674187876</v>
+        <v>-0.0343591027307208</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.0572429925122234</v>
+        <v>0.06109116365350288</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.06139322909036381</v>
+        <v>0.03900931923553348</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
@@ -6414,22 +6414,22 @@
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.1098160971600999</v>
+        <v>-0.08213699266959221</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.04264850198201325</v>
+        <v>0.0677845703696045</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.02250967222110322</v>
+        <v>0.004623575912254578</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
@@ -6441,22 +6441,22 @@
         <v>-0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.04876772135973712</v>
+        <v>-0.04831306205477564</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.03129694248774936</v>
+        <v>0.01895463123994841</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.05686850196846879</v>
+        <v>-0.06403470108709046</v>
       </c>
       <c r="DJ11" t="n">
         <v>-0</v>
@@ -6471,22 +6471,22 @@
         <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.0529347315939893</v>
+        <v>-0.05168392390520272</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.03819526359363664</v>
+        <v>0.009731400996332797</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.06753247676529003</v>
+        <v>-0.01164027511751624</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6498,55 +6498,55 @@
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.05069679079969618</v>
+        <v>0.06067303997722138</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.0004791776717347006</v>
+        <v>0.04031713473240757</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.08424553676311637</v>
+        <v>-0.01104128145985585</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
         <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
         <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.08860033367625435</v>
+        <v>-0.05795070585577409</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.03527958416208606</v>
+        <v>0.05810261972103166</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0414695461041819</v>
+        <v>0.006949270686383006</v>
       </c>
       <c r="EK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
@@ -6555,22 +6555,22 @@
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.06373952078818704</v>
+        <v>-0.01915467103030771</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.02958889561511986</v>
+        <v>0.06304237279659804</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.02590612646610323</v>
+        <v>-0.03499441472743254</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
@@ -6582,16 +6582,16 @@
         <v>0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1063954769510717</v>
+        <v>-0.09812577952470258</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.03154461820912657</v>
+        <v>0.07745410395224069</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.008540606609990209</v>
+        <v>-0.009184364066309958</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
@@ -6603,85 +6603,85 @@
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.03299478282619586</v>
+        <v>-0.04039971092523954</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.07081410395598503</v>
+        <v>0.05365267872968615</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.03742151106235899</v>
+        <v>-0.009543277036114307</v>
       </c>
       <c r="FL11" t="n">
         <v>-0</v>
       </c>
       <c r="FM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN11" t="n">
         <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0002471235973005015</v>
+        <v>0.0006578444078193274</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.05072207158088749</v>
+        <v>0.08330142363918275</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.00209314617086632</v>
+        <v>-0.002713221827410956</v>
       </c>
       <c r="FU11" t="n">
         <v>-0</v>
       </c>
       <c r="FV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX11" t="n">
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.0006301911071099038</v>
+        <v>-0.0525382725295921</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0.04750498586788761</v>
+        <v>0.02553852915782859</v>
       </c>
       <c r="GC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
         <v>-0</v>
@@ -6692,19 +6692,19 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7964118127581884</v>
+        <v>0.3852747516403544</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.09086433714969991</v>
+        <v>0.1681421643438565</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5819459345578362</v>
+        <v>-0.2827499894669469</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -6719,25 +6719,25 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.59896686164256</v>
+        <v>0.5418569108221308</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.00222497655747712</v>
+        <v>0.1045562931266838</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6135549132693022</v>
+        <v>-0.2393940327310151</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -6746,7 +6746,7 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0994347738963593</v>
+        <v>0.1388370767541995</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -6755,52 +6755,52 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.1373717176437401</v>
+        <v>-0.1438542992156231</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.02963166551204573</v>
+        <v>-0.003779572944529707</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.0286467359465614</v>
+        <v>0.006606515663117349</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.001362222066248693</v>
+        <v>-0.03911722465268537</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.004380117734815604</v>
+        <v>-0.0274247501619932</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.1431995457047099</v>
+        <v>0.09913499781252334</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
@@ -6809,13 +6809,13 @@
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0934474908494287</v>
+        <v>-0.05245191929859357</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.1662667612174096</v>
+        <v>-0.2753161336566085</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
@@ -6824,37 +6824,37 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.6913827163747037</v>
+        <v>0.7690800475255518</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.1560368564185206</v>
+        <v>-0.006726260025254798</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.5390360036726252</v>
+        <v>-0.2277559442725764</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.2649955939927354</v>
+        <v>-0.09229529774901679</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,16 +6863,16 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1299839734002849</v>
+        <v>-0.167576615469813</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.1399278472162197</v>
+        <v>-0.2706781005165382</v>
       </c>
       <c r="BI12" t="n">
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,22 +6881,22 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1846170643849217</v>
+        <v>0.2133941889469704</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.02332790751119772</v>
+        <v>0.2135637327194612</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0.01696513484835159</v>
+        <v>0.006571001231147539</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>0</v>
@@ -6905,28 +6905,28 @@
         <v>-0</v>
       </c>
       <c r="BU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.3818185231133373</v>
+        <v>0.454069224170851</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.1008290734541483</v>
+        <v>-0.03713624357026159</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.3432558246397133</v>
+        <v>-0.1793608523782347</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6935,49 +6935,49 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1617628431648664</v>
+        <v>-0.1774617011269715</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.04305213850584206</v>
+        <v>0.01282855669546759</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.1479100399775453</v>
+        <v>0.1145267093905429</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.01999831522312402</v>
+        <v>-0.2362143538949179</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.01810434378996758</v>
+        <v>0.114794263232404</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.01433723753361941</v>
+        <v>0.1514071764083188</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6989,88 +6989,88 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.1418498407857816</v>
+        <v>-0.1813162495404846</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.0333425183063918</v>
+        <v>-0.0661045950892131</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.1721574617030762</v>
+        <v>0.1056164555424571</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.03007819764473982</v>
+        <v>-0.05595974015616562</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.09372143481757716</v>
+        <v>-0.136234996044521</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0.05607047542927979</v>
+        <v>0.09070253646908333</v>
       </c>
       <c r="DK12" t="n">
         <v>0</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.04304834030855971</v>
+        <v>-0.04914370022264047</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.07077062274660034</v>
+        <v>-0.07280341453552391</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.005730752271658217</v>
+        <v>0.03785586139023178</v>
       </c>
       <c r="DT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW12" t="n">
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.02249378595618741</v>
+        <v>0.08141908921297923</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
@@ -7079,13 +7079,13 @@
         <v>0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.01395984722462919</v>
+        <v>-0.04251204130474136</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.08874602788966204</v>
+        <v>0.02416344770423848</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
@@ -7094,91 +7094,91 @@
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.125654166993829</v>
+        <v>0.001229824826854145</v>
       </c>
       <c r="EH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI12" t="n">
         <v>-0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0440789128758807</v>
+        <v>-0.1838623371058235</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.1828894978124812</v>
+        <v>-0.002429242844794428</v>
       </c>
       <c r="EL12" t="n">
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
         <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.06284333090566289</v>
+        <v>-0.05474846046116916</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.002036299591553622</v>
+        <v>-0.1244808768185864</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.06216839031102195</v>
+        <v>0.1451592417675694</v>
       </c>
       <c r="EU12" t="n">
         <v>-0</v>
       </c>
       <c r="EV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX12" t="n">
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.12762815647499</v>
+        <v>-0.1917198984863033</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.04138200108062681</v>
+        <v>-0.07902607749608986</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.136985255872985</v>
+        <v>0.1027613557527188</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.1131955235146625</v>
+        <v>-0.2236571863264372</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
@@ -7187,25 +7187,25 @@
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.01611442995717626</v>
+        <v>0.1637099958530934</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0.11093078758509</v>
+        <v>-0.1417738177838479</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.03026185605095724</v>
+        <v>-0.03371955755751735</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,10 +7214,10 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.0004225041839437869</v>
+        <v>0.001425505031693321</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.09198999692660896</v>
+        <v>0.03662399312789265</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
@@ -7229,22 +7229,22 @@
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.06347507027416607</v>
+        <v>-0.03553068452180683</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.04024948816024432</v>
+        <v>-0.04865686602911655</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,24 +7253,24 @@
         <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.2054182648188196</v>
+        <v>-0.1929201256967754</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8708346060688317</v>
+        <v>0.4023966218356095</v>
       </c>
       <c r="C13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2142746893700131</v>
+        <v>-0.05101994138788359</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -7285,10 +7285,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2799874130475208</v>
+        <v>-0.1800726958004464</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6767748172759319</v>
+        <v>0.5579021415315049</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,34 +7297,34 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3187142043889502</v>
+        <v>-0.0799398428291699</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.08661850518539095</v>
+        <v>0.02740154707800468</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3190199761263086</v>
+        <v>0.02721807348390089</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0626094823326163</v>
+        <v>-0.3113000880014426</v>
       </c>
       <c r="X13" t="n">
         <v>-0</v>
@@ -7333,97 +7333,97 @@
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.03191548760864131</v>
+        <v>0.008569169304965313</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.06910573859886571</v>
+        <v>0.03578455284497386</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.02205537429460202</v>
+        <v>-0.1027052024919446</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.1400774738195134</v>
+        <v>-0.0276983974856288</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.2352246845127236</v>
+        <v>0.1744784671578248</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.03298982604353295</v>
+        <v>-0.2594710925325196</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.05762307067448197</v>
+        <v>-0.1687335946169874</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.875061822051338</v>
+        <v>0.3837748742868765</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.2161073808240018</v>
+        <v>-0.3088135557539683</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0.03588018947950909</v>
+        <v>0.1472745604286941</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.07037043495076531</v>
+        <v>0.2016103010769171</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,25 +7432,25 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.4494821724056719</v>
+        <v>0.1415274703000157</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.07468026564367429</v>
+        <v>-0.06155442537366967</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1406940318167552</v>
+        <v>0.134990446962665</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
@@ -7459,7 +7459,7 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.2247006743119875</v>
+        <v>0.2961839608940663</v>
       </c>
       <c r="BQ13" t="n">
         <v>-0</v>
@@ -7474,19 +7474,19 @@
         <v>-0</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.06732868385898753</v>
+        <v>-0.0446885345300736</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.5501306223652715</v>
+        <v>0.2119559026278432</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.04883144363337718</v>
+        <v>-0.1966103731515685</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -7501,10 +7501,10 @@
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.02749564617644119</v>
+        <v>0.1011350725784223</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1686842339307597</v>
+        <v>-0.1035452507533197</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
@@ -7513,10 +7513,10 @@
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0197272061931873</v>
+        <v>0.04135039936018171</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ13" t="n">
         <v>-0</v>
@@ -7525,49 +7525,49 @@
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>-0.2045427968028335</v>
+        <v>-0.03794760846294822</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.04250451396838024</v>
+        <v>-0.1663297483435719</v>
       </c>
       <c r="CO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.1085070874375753</v>
+        <v>0.0306439628530062</v>
       </c>
       <c r="CR13" t="n">
         <v>-0</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.03503953057976069</v>
+        <v>0.09294009304622509</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.1698249251277801</v>
+        <v>-0.1139477541196344</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.009188400521714062</v>
+        <v>0.01615891505618677</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
@@ -7582,19 +7582,19 @@
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0.0795071851972947</v>
+        <v>0.02325018049159065</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.2854670806193816</v>
+        <v>0.001679353764721113</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.07358401405962407</v>
+        <v>-0.08837743017727334</v>
       </c>
       <c r="DJ13" t="n">
         <v>0</v>
@@ -7606,13 +7606,13 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0.03340661527867997</v>
+        <v>0.04524384757547482</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.1247152244115288</v>
+        <v>-0.1859282033324317</v>
       </c>
       <c r="DP13" t="n">
         <v>-0</v>
@@ -7621,37 +7621,37 @@
         <v>-0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.01035108343026999</v>
+        <v>-0.05607117268826861</v>
       </c>
       <c r="DS13" t="n">
         <v>-0</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0.00973104769102923</v>
+        <v>-0.05742022887915128</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.2643601141036239</v>
+        <v>-0.2512651748503514</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.2154811434489977</v>
+        <v>-0.1714676485840519</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
@@ -7663,46 +7663,46 @@
         <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>-0.01608947852282232</v>
+        <v>0.06242824547064451</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.0003054533236781663</v>
+        <v>0.01046149172845883</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.02745323490744002</v>
+        <v>-0.03067804879193332</v>
       </c>
       <c r="EK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.02867579761596263</v>
+        <v>0.06038715370459682</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.1183527922792776</v>
+        <v>-0.01010429022073295</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
       </c>
       <c r="ER13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.111128806208741</v>
+        <v>0.01164279584835305</v>
       </c>
       <c r="ET13" t="n">
         <v>-0</v>
@@ -7717,19 +7717,19 @@
         <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.03067738597420665</v>
+        <v>0.1139228746596141</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.1588236290144562</v>
+        <v>-0.1275561567229381</v>
       </c>
       <c r="EZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.02351500576458665</v>
+        <v>0.006259812204716372</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
@@ -7741,28 +7741,28 @@
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.03019476664699346</v>
+        <v>0.01958500179665097</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.07313444762629849</v>
+        <v>-0.1611419704399782</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.08511835088412915</v>
+        <v>-0.07558003184553275</v>
       </c>
       <c r="FL13" t="n">
         <v>0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
         <v>-0</v>
@@ -7771,19 +7771,19 @@
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0001899868233847223</v>
+        <v>0.001860110354135501</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.09600406308637605</v>
+        <v>0.03839352047272634</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.03288911514837847</v>
+        <v>0.04946879325108581</v>
       </c>
       <c r="FU13" t="n">
         <v>-0</v>
@@ -7792,16 +7792,16 @@
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
         <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0.2033111233342238</v>
+        <v>0.01365096535954397</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.009227584742770667</v>
+        <v>0.009995939023296697</v>
       </c>
       <c r="GA13" t="n">
         <v>-0</v>
@@ -7813,7 +7813,7 @@
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,7 +7822,7 @@
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1719540176490533</v>
+        <v>0.3100159468294384</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -7839,10 +7839,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.05510748947682456</v>
+        <v>0.06811120432950202</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.08715665807871681</v>
+        <v>-0.1611041023914769</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
@@ -7854,10 +7854,10 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1390656461686944</v>
+        <v>0.3933133250076254</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -7866,16 +7866,16 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.02624024872693008</v>
+        <v>-0.05829223161404149</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.07232889606455117</v>
+        <v>-0.1864319653107201</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -7884,49 +7884,49 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.02727864124550647</v>
+        <v>0.1339420394090474</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.01982417378577795</v>
+        <v>-0.04676546405744341</v>
       </c>
       <c r="X14" t="n">
-        <v>0.00177633182022937</v>
+        <v>-0.0005520063346231733</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.003768989232316697</v>
+        <v>-0.01381869985767347</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.00501737195938803</v>
+        <v>-0.06484855263153887</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.002169836679830884</v>
+        <v>0.01799787771950286</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>-0</v>
@@ -7938,34 +7938,34 @@
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.02590748447132112</v>
+        <v>0.08563412067092957</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0008909777968175589</v>
+        <v>-0.03916690223177431</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.04164852344248137</v>
+        <v>-0.04927568746796703</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
         <v>-0</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.1271298540695137</v>
+        <v>0.582070555182156</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
@@ -7974,25 +7974,25 @@
         <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.03770247805047881</v>
+        <v>-0.2317705639356958</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.09526868018307566</v>
+        <v>-0.2360066015405801</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
         <v>-0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC14" t="n">
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.03604310439482949</v>
+        <v>-0.1412913627122537</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -8001,106 +8001,106 @@
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.03919740946567946</v>
+        <v>0.01172857157645602</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.02183761878672415</v>
+        <v>-0.06330069356572139</v>
       </c>
       <c r="BI14" t="n">
         <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.03191466590888783</v>
+        <v>0.1317949683534462</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
         <v>-0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.003310019553334726</v>
+        <v>0.07966873889276965</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.008157693347078132</v>
+        <v>0.02499458703803637</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.07007692543435005</v>
+        <v>0.311414107391049</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
         <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.02844187206118379</v>
+        <v>-0.05773175388937433</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0.02748117557111489</v>
+        <v>-0.09267839471568112</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD14" t="n">
         <v>0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.03525370561808943</v>
+        <v>-0.1264526959990391</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
         <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0008299013390268792</v>
+        <v>0.01543443378994865</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.02571409301663053</v>
+        <v>0.04786293207660536</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.003508196526299338</v>
+        <v>-0.1484235205822863</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
@@ -8109,37 +8109,37 @@
         <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.003662989812347138</v>
+        <v>0.1087592152210064</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0.02252779228620241</v>
+        <v>0.03336387973319571</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
         <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.03222189101000417</v>
+        <v>-0.1203053099527209</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
         <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.002035440516834429</v>
+        <v>-0.009253540863334591</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.03141525101889747</v>
+        <v>0.08180846623758554</v>
       </c>
       <c r="DB14" t="n">
         <v>0</v>
@@ -8148,40 +8148,40 @@
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.02464504027803544</v>
+        <v>-0.1166518942729981</v>
       </c>
       <c r="DG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.04390092452442424</v>
+        <v>-0.1717712997393305</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0.000415718521753898</v>
+        <v>0.05067825537158664</v>
       </c>
       <c r="DK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.0112438305052271</v>
+        <v>-0.06995829549528715</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
@@ -8190,37 +8190,37 @@
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.01783998545642576</v>
+        <v>0.01555041194180345</v>
       </c>
       <c r="DS14" t="n">
-        <v>-1.520451815036939e-05</v>
+        <v>0.07062148928896106</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.02362827017215603</v>
+        <v>-0.1114566189214003</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
         <v>-0</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.006528698083716571</v>
+        <v>0.009111141093780377</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.012803167295742</v>
+        <v>0.02823263846278938</v>
       </c>
       <c r="EC14" t="n">
         <v>0</v>
@@ -8229,25 +8229,25 @@
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
         <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.03508480927577015</v>
+        <v>-0.0354489578088179</v>
       </c>
       <c r="EH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI14" t="n">
         <v>-0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.01182183706424115</v>
+        <v>-0.03623872431755571</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.03338423356741664</v>
+        <v>-0.03767154240204373</v>
       </c>
       <c r="EL14" t="n">
         <v>-0</v>
@@ -8262,22 +8262,22 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.0211354864433247</v>
+        <v>-0.0130880037112671</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
         <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.007802926414176778</v>
+        <v>-0.08802217275359603</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.006600795818346028</v>
+        <v>-0.01793812027157698</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
@@ -8289,46 +8289,46 @@
         <v>0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.02995722307648519</v>
+        <v>-0.1512773396245544</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
         <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.002203834215592546</v>
+        <v>-0.0127472065120183</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.02706645431695889</v>
+        <v>0.0604761911094209</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.001231492219864073</v>
+        <v>0.09690481661052079</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.009410707390329997</v>
+        <v>-0.02623287152169475</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.02954821090179123</v>
+        <v>0.1271336068629508</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
@@ -8340,10 +8340,10 @@
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.001983613360450768</v>
+        <v>-0.02284104427554435</v>
       </c>
       <c r="FR14" t="n">
         <v>-0</v>
@@ -8352,43 +8352,43 @@
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.01128133942941411</v>
+        <v>0.06178755696227989</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.01844022066727466</v>
+        <v>-0.09293733920215562</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.005415781100468099</v>
+        <v>-0.04592804335817525</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
         <v>0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0.02005812897815362</v>
+        <v>0.08713129147864047</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
         <v>-0</v>
@@ -8399,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1057968697325088</v>
+        <v>0.169065790212127</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -8408,37 +8408,37 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.08475484688763088</v>
+        <v>-0.05066034267543727</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.02057865388933401</v>
+        <v>-0.0492492105172555</v>
       </c>
       <c r="G15" t="n">
         <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.07480445114314249</v>
+        <v>0.1865473395647892</v>
       </c>
       <c r="L15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.06648916123669923</v>
+        <v>-0.08425672573086003</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.02522494392780352</v>
+        <v>-0.06334587307873651</v>
       </c>
       <c r="P15" t="n">
         <v>-0</v>
@@ -8450,49 +8450,49 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01906094125911958</v>
+        <v>0.06023724467500365</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.004191752753759134</v>
+        <v>-0.05267309116892206</v>
       </c>
       <c r="X15" t="n">
-        <v>0.01180110368614054</v>
+        <v>0.002023197367531834</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.003272045536479402</v>
+        <v>-0.01760236852532795</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.002587517684227683</v>
+        <v>-0.0577588608007779</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.00231735278533981</v>
+        <v>0.005667795359072101</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
@@ -8504,37 +8504,37 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.01806452962940453</v>
+        <v>0.01907790185305228</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.01243386786388016</v>
+        <v>-0.03279324789573839</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.01228520317475038</v>
+        <v>0.006009324699997425</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.09027327901085329</v>
+        <v>0.2047505535943754</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
@@ -8543,25 +8543,25 @@
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.05113521881706509</v>
+        <v>-0.122566255077423</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.01129680401635391</v>
+        <v>-0.0875325502405213</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
         <v>-0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.01919559861795131</v>
+        <v>-0.02164178361000426</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -8570,64 +8570,64 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.04969339796314527</v>
+        <v>-0.01232337492912886</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.01919363218217901</v>
+        <v>-0.00444542915371853</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.02558812258889233</v>
+        <v>0.03142857731603116</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.01396521779819443</v>
+        <v>0.05551157567144697</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.0217762928690108</v>
+        <v>0.002868336026333868</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.04866710589721925</v>
+        <v>0.1262015038498201</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.02364773077474541</v>
+        <v>-0.04144153277037738</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.001996118077983738</v>
+        <v>-0.02918084037244212</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
@@ -8642,34 +8642,34 @@
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.01760819412881975</v>
+        <v>-0.04432926185321448</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.01222752609177812</v>
+        <v>0.02828454650189088</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.007245793073079688</v>
+        <v>0.02244905793340447</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>-0</v>
       </c>
       <c r="CL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.0002141957200115257</v>
+        <v>-0.0318874636945167</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
@@ -8678,40 +8678,40 @@
         <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.003925178938257989</v>
+        <v>0.05526558969804204</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.003646202967627068</v>
+        <v>0.01671105001416602</v>
       </c>
       <c r="CS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.01094687758772159</v>
+        <v>-0.04542752808449991</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.009415954308945634</v>
+        <v>0.02493848444848961</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.01312032000253682</v>
+        <v>0.03762893299077263</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
         <v>0</v>
@@ -8723,19 +8723,19 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.01631896342086048</v>
+        <v>-0.03983530717061545</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.01846983431862562</v>
+        <v>-0.04095832388797412</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0.003693580578417738</v>
+        <v>0.0159250373701761</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
@@ -8744,40 +8744,40 @@
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.008041331963759196</v>
+        <v>0.007897533915924355</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.01979462192430372</v>
+        <v>-0.02882831525024543</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0.01366813514594768</v>
+        <v>-0.001330311087722285</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.01512565863019831</v>
+        <v>-0.01099574836975101</v>
       </c>
       <c r="DY15" t="n">
         <v>0</v>
@@ -8786,16 +8786,16 @@
         <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.01340477666797229</v>
+        <v>-0.01852168617847985</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.001415198527650156</v>
+        <v>-0.001732339243399531</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE15" t="n">
         <v>-0</v>
@@ -8804,22 +8804,22 @@
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.01793955233745228</v>
+        <v>-0.0262911255668647</v>
       </c>
       <c r="EH15" t="n">
         <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.01082317761302391</v>
+        <v>0.02437037433461773</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.007110880765519101</v>
+        <v>0.0006051399637435671</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>-0</v>
@@ -8831,19 +8831,19 @@
         <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.0003538967037369907</v>
+        <v>-0.03077126215995603</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.008469124541862586</v>
+        <v>0.02736314960902176</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0.001591717708135629</v>
+        <v>0.05143346906447127</v>
       </c>
       <c r="EU15" t="n">
         <v>0</v>
@@ -8852,25 +8852,25 @@
         <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.01113163272902852</v>
+        <v>-0.05209393238056755</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
         <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.01147713504073795</v>
+        <v>0.01799644510432529</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.0145324386488448</v>
+        <v>0.02306254443938176</v>
       </c>
       <c r="FD15" t="n">
         <v>0</v>
@@ -8882,10 +8882,10 @@
         <v>-0</v>
       </c>
       <c r="FG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.002715196563887185</v>
+        <v>0.05484359754724453</v>
       </c>
       <c r="FI15" t="n">
         <v>-0</v>
@@ -8894,16 +8894,16 @@
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.01351145408553161</v>
+        <v>-0.03642639001315871</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.01047446064001669</v>
+        <v>0.04090037014279284</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
@@ -8912,52 +8912,52 @@
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.002701188916824334</v>
+        <v>-0.0167414066059839</v>
       </c>
       <c r="FR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS15" t="n">
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.008326859423344778</v>
+        <v>0.02974479920288671</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.0120175413229906</v>
+        <v>-0.03288490210535657</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.0005504205876127753</v>
+        <v>-0.04698836091928854</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
         <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.01311505274425613</v>
+        <v>0.04041042830583202</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG15" t="n">
         <v>0</v>
@@ -8968,46 +8968,46 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4153572051450508</v>
+        <v>0.2561772895102798</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1527524371230786</v>
+        <v>-0.1750014830929682</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.05337349798471756</v>
+        <v>-0.01707228129826151</v>
       </c>
       <c r="F16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3239443995061827</v>
+        <v>0.3310243202847041</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1895680220001493</v>
+        <v>-0.2530986344472804</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.06892823910276677</v>
+        <v>-0.07292901125943244</v>
       </c>
       <c r="O16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>-0</v>
@@ -9019,22 +9019,22 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.102082386197136</v>
+        <v>0.05356350450260748</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.01067781167138243</v>
+        <v>-0.04687319317016449</v>
       </c>
       <c r="W16" t="n">
-        <v>0.09840651620137804</v>
+        <v>-0.03705709661439411</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
@@ -9043,49 +9043,49 @@
         <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1042984366478261</v>
+        <v>-0.0168642603143915</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.008280249905984419</v>
+        <v>-0.02899412825898812</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.007868876847546148</v>
+        <v>-0.0150814432286299</v>
       </c>
       <c r="AG16" t="n">
         <v>-0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.01413306067264882</v>
+        <v>0.05757216167317508</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.06963297121984609</v>
+        <v>-0.06238822091384541</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.09327890535983155</v>
+        <v>0.03596742762678435</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
@@ -9097,31 +9097,31 @@
         <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.3350417824791784</v>
+        <v>0.2404149541552711</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0.0582899494006054</v>
+        <v>-0.145423785059637</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.1352134909149114</v>
+        <v>-0.1338746695358506</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
         <v>-0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
@@ -9130,25 +9130,25 @@
         <v>-0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.03028057937233576</v>
+        <v>-0.007752149394776846</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>-0.06014711045112877</v>
+        <v>-0.04414746632039725</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1089048352468886</v>
+        <v>0.02384365208788119</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
@@ -9157,16 +9157,16 @@
         <v>-0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.05861349550282345</v>
+        <v>-0.0008410011251675629</v>
       </c>
       <c r="BN16" t="n">
         <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.0575667306426512</v>
+        <v>0.09645894003761352</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.1982779608751278</v>
+        <v>0.01307952018555015</v>
       </c>
       <c r="BQ16" t="n">
         <v>-0</v>
@@ -9178,55 +9178,55 @@
         <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.1635072823828878</v>
+        <v>0.1698814881300876</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.01661427909170024</v>
+        <v>-0.1458391754460469</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.09747195118235644</v>
+        <v>-0.005598778551234183</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.09299382153137263</v>
+        <v>-0.07666697059516209</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.02466341910762236</v>
+        <v>0.1084906814593476</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.01222205628045068</v>
+        <v>0.008496451031540524</v>
       </c>
       <c r="CI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
@@ -9238,49 +9238,49 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.03087720610851103</v>
+        <v>-0.07823351359508972</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0.07622409350281764</v>
+        <v>0.1166813786195598</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.136309073103893</v>
+        <v>0.04055031482710982</v>
       </c>
       <c r="CR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
       </c>
       <c r="CT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.08923844109489036</v>
+        <v>-0.08682244662341965</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.04471339974487957</v>
+        <v>0.1254738101017041</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.004810092314039812</v>
+        <v>0.01084953685973634</v>
       </c>
       <c r="DA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
         <v>-0</v>
@@ -9292,16 +9292,16 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.008880697775690335</v>
+        <v>-0.02695985563480279</v>
       </c>
       <c r="DG16" t="n">
         <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.003708755479479001</v>
+        <v>0.01093239612189692</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.002878872980683219</v>
+        <v>-0.03487059043924402</v>
       </c>
       <c r="DJ16" t="n">
         <v>-0</v>
@@ -9316,22 +9316,22 @@
         <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.01040306623990542</v>
+        <v>-0.07519457440914891</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0.1684177412083869</v>
+        <v>0.0438662129144749</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.03684732392055023</v>
+        <v>0.01566541962965003</v>
       </c>
       <c r="DS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
@@ -9340,82 +9340,82 @@
         <v>-0</v>
       </c>
       <c r="DV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.06528869013948503</v>
+        <v>-0.003432475501874451</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.01647540544408062</v>
+        <v>-0.01314104424326174</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.01696301540797479</v>
+        <v>-0.03449910040350194</v>
       </c>
       <c r="EB16" t="n">
         <v>0</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.1170385087711713</v>
+        <v>-0.05154199724513816</v>
       </c>
       <c r="EH16" t="n">
         <v>0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.08252476119456385</v>
+        <v>0.07848901072739527</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.07755929381076397</v>
+        <v>0.0348342930062163</v>
       </c>
       <c r="EK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
       </c>
       <c r="EN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.08683023244737859</v>
+        <v>-0.02209216035294274</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.06773080070714632</v>
+        <v>0.07825511185941922</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.01989386463468211</v>
+        <v>-0.01497028819188232</v>
       </c>
       <c r="ET16" t="n">
         <v>0</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
@@ -9424,46 +9424,46 @@
         <v>-0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.08395258427681976</v>
+        <v>-0.09368032424183863</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.02768983226285621</v>
+        <v>0.123554136443522</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.004075162106430106</v>
+        <v>0.01331652200640048</v>
       </c>
       <c r="FC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD16" t="n">
         <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF16" t="n">
         <v>-0</v>
       </c>
       <c r="FG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.02981761782796473</v>
+        <v>0.0692475196620234</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
-        <v>-0.07811525575997685</v>
+        <v>-0.1447210542788393</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.03957293323877484</v>
+        <v>0.01484784457313872</v>
       </c>
       <c r="FL16" t="n">
         <v>-0</v>
@@ -9475,22 +9475,22 @@
         <v>0</v>
       </c>
       <c r="FO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.006028435789170863</v>
+        <v>-0.04293328085521802</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.1084392961027306</v>
+        <v>0.07866008797769514</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.005669346021173258</v>
+        <v>0.03681617316414271</v>
       </c>
       <c r="FU16" t="n">
         <v>-0</v>
@@ -9499,37 +9499,37 @@
         <v>0</v>
       </c>
       <c r="FW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX16" t="n">
         <v>0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.01330668224531322</v>
+        <v>-0.0165711092709719</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0.0646767419494222</v>
+        <v>0.0345974475000691</v>
       </c>
       <c r="GC16" t="n">
         <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -10106,19 +10106,19 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1955844602962666</v>
+        <v>0.7878633203216263</v>
       </c>
       <c r="C18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0573237275039872</v>
+        <v>0.1753757439169801</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1176689356884328</v>
+        <v>-0.2848025707500379</v>
       </c>
       <c r="G18" t="n">
         <v>-0</v>
@@ -10127,40 +10127,40 @@
         <v>-0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1725380383146246</v>
+        <v>1.052020991432592</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.03145811373663959</v>
+        <v>-0.02868449116591235</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1173016771310044</v>
+        <v>-0.2635062595567315</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.02088460486761182</v>
+        <v>0.2079886283190378</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -10169,16 +10169,16 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.01640005628446425</v>
+        <v>-0.08988934089694015</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.001993725783814916</v>
+        <v>-0.03733567909227709</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -10187,22 +10187,22 @@
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.001356453217562624</v>
+        <v>0.02773102369761076</v>
       </c>
       <c r="AD18" t="n">
         <v>-0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.01935586411750067</v>
+        <v>-0.3836868560917128</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.0002807767392033485</v>
+        <v>-0.06763825322011548</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>-0</v>
@@ -10214,7 +10214,7 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.02453327275050268</v>
+        <v>0.1946461235988402</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
@@ -10223,10 +10223,10 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.004011956251488029</v>
+        <v>0.004040885704422371</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.03186811951592929</v>
+        <v>-0.088055344967441</v>
       </c>
       <c r="AQ18" t="n">
         <v>-0</v>
@@ -10238,10 +10238,10 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.1182207341344241</v>
+        <v>0.9356747488995848</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
@@ -10250,79 +10250,79 @@
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.01706000986491803</v>
+        <v>-0.2145807810634514</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.0622545558779858</v>
+        <v>-0.1358086835724432</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.03487884350627186</v>
+        <v>-0.09620385774168327</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.04686936049584645</v>
+        <v>-0.1128013532478385</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.04431923995765664</v>
+        <v>-0.1497521574502735</v>
       </c>
       <c r="BI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
         <v>-0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.03312529975264238</v>
+        <v>0.1497531676924427</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO18" t="n">
         <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.003557253501918739</v>
+        <v>0.02932298932774973</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.01915244502906337</v>
+        <v>-0.04570139209666776</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
         <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
         <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.0602171278281084</v>
+        <v>0.5668626715363552</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
@@ -10331,10 +10331,10 @@
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.01864234103097717</v>
+        <v>-0.03867182932408814</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0.04035080286368642</v>
+        <v>-0.1926619328002012</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
@@ -10349,154 +10349,154 @@
         <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.03091895479689228</v>
+        <v>-0.2621310381608715</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.002999741711921904</v>
+        <v>0.03875378378788715</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.02745837148458497</v>
+        <v>0.1125435231158723</v>
       </c>
       <c r="CJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK18" t="n">
         <v>0</v>
       </c>
       <c r="CL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM18" t="n">
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.00736323709553628</v>
+        <v>-0.4206053496293856</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.01337612968087371</v>
+        <v>0.2412518257946932</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.008538606990017008</v>
+        <v>0.1373299599268796</v>
       </c>
       <c r="CS18" t="n">
         <v>-0</v>
       </c>
       <c r="CT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.02406000500622384</v>
+        <v>-0.2355637327233895</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.006775498304454394</v>
+        <v>-0.02538272437477521</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.03280272960414036</v>
+        <v>0.144313813824928</v>
       </c>
       <c r="DB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC18" t="n">
         <v>-0</v>
       </c>
       <c r="DD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.01228768337052847</v>
+        <v>-0.05974332068089105</v>
       </c>
       <c r="DG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.03094020918752625</v>
+        <v>-0.3772494412608997</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.0001226839614979743</v>
+        <v>0.0705458071498398</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
       </c>
       <c r="DL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.006795211005618329</v>
+        <v>-0.1019115115004232</v>
       </c>
       <c r="DP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ18" t="n">
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.0307923293361752</v>
+        <v>0.0009387559614029015</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.0004612995519719142</v>
+        <v>-0.03777027794315943</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW18" t="n">
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.01377460250652974</v>
+        <v>-0.03195515761340013</v>
       </c>
       <c r="DY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ18" t="n">
         <v>-0</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.004741634155976387</v>
+        <v>-0.2125355220908846</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.01780713693393893</v>
+        <v>0.1005985311688274</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
@@ -10508,37 +10508,37 @@
         <v>-0</v>
       </c>
       <c r="EF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.03293124787782795</v>
+        <v>-0.06804950097864934</v>
       </c>
       <c r="EH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI18" t="n">
         <v>0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.00304971769285448</v>
+        <v>-0.1232623316891327</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.02741264553479034</v>
+        <v>0.0244671423088197</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
         <v>-0</v>
       </c>
       <c r="EN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO18" t="n">
         <v>0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.01162491910939762</v>
+        <v>-0.05713902585655186</v>
       </c>
       <c r="EQ18" t="n">
         <v>0</v>
@@ -10547,70 +10547,70 @@
         <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>-0.01449646432241165</v>
+        <v>-0.1078659820456623</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.01451631036138486</v>
+        <v>0.04829185494511695</v>
       </c>
       <c r="EU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.02235811953906987</v>
+        <v>-0.2770526568463335</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
         <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>-0.004649318084795771</v>
+        <v>-0.06955994564503337</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.03077857441642638</v>
+        <v>0.1307979196548326</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
       </c>
       <c r="FF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH18" t="n">
-        <v>0.002722592043912259</v>
+        <v>0.3173173310531133</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.008630068950705883</v>
+        <v>-0.1927178963482096</v>
       </c>
       <c r="FL18" t="n">
-        <v>-0.02239772934934034</v>
+        <v>-0.2770468636342763</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
         <v>0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.003555128235483988</v>
+        <v>-0.1569485778581266</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
@@ -10628,46 +10628,46 @@
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.003938254028870664</v>
+        <v>0.07158514427785638</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.03465978461921009</v>
+        <v>-0.2219408003871606</v>
       </c>
       <c r="FV18" t="n">
         <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.01840337407645683</v>
+        <v>0.02764576239744682</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
         <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.01639096137968626</v>
+        <v>0.05844353895394877</v>
       </c>
       <c r="GE18" t="n">
         <v>-0</v>
       </c>
       <c r="GF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
